--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 16,08,26 лгрсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 16,08,26 лгрсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021BE779-D6DA-4849-B31F-452C6BAEDF7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29436AA5-9156-4E2B-AEDB-50BC09B96468}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
